--- a/old/260711.xlsx
+++ b/old/260711.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9FDFCF-6DE3-43E8-9A64-A0DF9ECDDEEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52EBFEB2-339E-474A-AC1C-2B032719799C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10470" yWindow="2250" windowWidth="15030" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="4" r:id="rId2"/>
     <sheet name="Sheet4" sheetId="5" r:id="rId3"/>
-    <sheet name="SheetX" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -103,16 +102,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -487,31 +480,4 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="26.33203125" customWidth="1"/>
-    <col min="2" max="3" width="28.9140625" customWidth="1"/>
-    <col min="4" max="4" width="16.08203125" customWidth="1"/>
-    <col min="5" max="5" width="26.1640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="3"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/old/260711.xlsx
+++ b/old/260711.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52EBFEB2-339E-474A-AC1C-2B032719799C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD3B3FA-3FAB-4BB7-A98B-7D5C31958629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10470" yWindow="2250" windowWidth="15030" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10570" yWindow="4110" windowWidth="15030" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -27,13 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>auch Ideen</t>
-  </si>
-  <si>
-    <t>wie es so schön heißt</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Erinnerung rufen</t>
   </si>
@@ -387,35 +381,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF013D0-15FD-4230-B377-278FFE076B7D}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A3:A5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -434,22 +418,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -468,12 +452,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
